--- a/docs/project_tracking/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/project_tracking/Unit_Test_Plan_v0.1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bibi Fatima\Downloads\Internship_artifacts\Internship_artifacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\infosys\ai-career-companion\docs\project_tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F004E9-5812-42BB-99DB-2E9F44B87BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA471FE1-7874-4EE3-96A7-C0A35F70E343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="173">
   <si>
     <t>Actual Result</t>
   </si>
@@ -373,6 +373,222 @@
   </si>
   <si>
     <t>M2 implementation was committed and pushed successfully to GitHub</t>
+  </si>
+  <si>
+    <t>Skill Gap API</t>
+  </si>
+  <si>
+    <t>Select a recommended job and call the Skill Gap endpoint</t>
+  </si>
+  <si>
+    <t>Valid profile and valid job ID available</t>
+  </si>
+  <si>
+    <t>Skill gap analysis should be generated for the selected job</t>
+  </si>
+  <si>
+    <t>Skill gap endpoint accepted the selected job and generated job-specific analysis</t>
+  </si>
+  <si>
+    <t>Invalid Skill Gap Job</t>
+  </si>
+  <si>
+    <t>Submit an invalid or placeholder job ID</t>
+  </si>
+  <si>
+    <t>Job ID does not exist in current job matches</t>
+  </si>
+  <si>
+    <t>System should return a meaningful validation/error response</t>
+  </si>
+  <si>
+    <t>System returned an error indicating that the requested job was not found</t>
+  </si>
+  <si>
+    <t>Strong Skill Identification</t>
+  </si>
+  <si>
+    <t>Run skill gap analysis for a candidate with matching skills</t>
+  </si>
+  <si>
+    <t>Candidate skills overlap with job requirements</t>
+  </si>
+  <si>
+    <t>Matching skills should be identified as strong matches</t>
+  </si>
+  <si>
+    <t>Matching skills were identified from candidate and job requirements</t>
+  </si>
+  <si>
+    <t>Missing Skill Identification</t>
+  </si>
+  <si>
+    <t>Run skill gap analysis against a job requiring skills absent from the resume</t>
+  </si>
+  <si>
+    <t>Required skill is not present in candidate profile</t>
+  </si>
+  <si>
+    <t>Missing skills should be identified</t>
+  </si>
+  <si>
+    <t>Missing skills were identified for the selected role</t>
+  </si>
+  <si>
+    <t>Partial Skill Identification</t>
+  </si>
+  <si>
+    <t>Analyze a candidate with related but incomplete skill evidence</t>
+  </si>
+  <si>
+    <t>Candidate has partial evidence of a required skill</t>
+  </si>
+  <si>
+    <t>Skill should be categorized as partially demonstrated where applicable</t>
+  </si>
+  <si>
+    <t>Partial skill information was processed by the skill-gap workflow</t>
+  </si>
+  <si>
+    <t>Skill Recommendation</t>
+  </si>
+  <si>
+    <t>Generate recommendations for identified skill gaps</t>
+  </si>
+  <si>
+    <t>Candidate has missing skills</t>
+  </si>
+  <si>
+    <t>System should provide actionable improvement recommendations</t>
+  </si>
+  <si>
+    <t>Recommendations were generated for identified gaps</t>
+  </si>
+  <si>
+    <t>Job-to-Skill-Gap Navigation</t>
+  </si>
+  <si>
+    <t>Click Analyze Skill Gap from a recommended job card</t>
+  </si>
+  <si>
+    <t>Recommended job is available</t>
+  </si>
+  <si>
+    <t>Selected job should be passed to Skill Gap analysis</t>
+  </si>
+  <si>
+    <t>Job selection was connected to the Skill Gap workflow</t>
+  </si>
+  <si>
+    <t>Redesigned Dashboard</t>
+  </si>
+  <si>
+    <t>Start frontend and open Career Companion dashboard</t>
+  </si>
+  <si>
+    <t>React/Vite frontend available</t>
+  </si>
+  <si>
+    <t>Dashboard should load with redesigned navigation and career sections</t>
+  </si>
+  <si>
+    <t>Recommended Job Cards</t>
+  </si>
+  <si>
+    <t>Open Recommended Jobs from dashboard</t>
+  </si>
+  <si>
+    <t>Profile and matching results available</t>
+  </si>
+  <si>
+    <t>Matching jobs should be displayed with scores and skills</t>
+  </si>
+  <si>
+    <t>Recommended jobs were displayed with match scores and skill information</t>
+  </si>
+  <si>
+    <t>Job Detail View</t>
+  </si>
+  <si>
+    <t>Select a recommended job</t>
+  </si>
+  <si>
+    <t>Job match exists</t>
+  </si>
+  <si>
+    <t>Job details, match information and available career actions should be displayed</t>
+  </si>
+  <si>
+    <t>Selected job information was displayed through the redesigned interface</t>
+  </si>
+  <si>
+    <t>Application Studio Navigation</t>
+  </si>
+  <si>
+    <t>Open Application Studio</t>
+  </si>
+  <si>
+    <t>Frontend navigation available</t>
+  </si>
+  <si>
+    <t>Application Studio should open</t>
+  </si>
+  <si>
+    <t>Application Studio section was added to the M3 interface</t>
+  </si>
+  <si>
+    <t>Interview Preparation Navigation</t>
+  </si>
+  <si>
+    <t>Open Interview Preparation</t>
+  </si>
+  <si>
+    <t>Interview preparation section should open</t>
+  </si>
+  <si>
+    <t>Interview Preparation section was added to the M3 interface</t>
+  </si>
+  <si>
+    <t>Career Assistant Navigation</t>
+  </si>
+  <si>
+    <t>Open Career Assistant</t>
+  </si>
+  <si>
+    <t>Career Assistant interface should open</t>
+  </si>
+  <si>
+    <t>Career Assistant section was added to the M3 interface</t>
+  </si>
+  <si>
+    <t>Backend Compatibility</t>
+  </si>
+  <si>
+    <t>Run frontend against FastAPI backend</t>
+  </si>
+  <si>
+    <t>Backend running on port 8000</t>
+  </si>
+  <si>
+    <t>Frontend should communicate with backend without breaking existing M2 APIs</t>
+  </si>
+  <si>
+    <t>Existing profile, resume and job matching workflows remained available</t>
+  </si>
+  <si>
+    <t>M2 Regression Test</t>
+  </si>
+  <si>
+    <t>Run profile, resume upload and job matching workflows after M3 changes</t>
+  </si>
+  <si>
+    <t>Existing M2 functionality available</t>
+  </si>
+  <si>
+    <t>M2 functionality should continue working after M3 implementation</t>
+  </si>
+  <si>
+    <t>Existing M2 workflows remained functional</t>
   </si>
 </sst>
 </file>
@@ -747,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -1157,6 +1373,306 @@
         <v>100</v>
       </c>
     </row>
+    <row r="21" spans="1:6" ht="66">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="66">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="66">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="66">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="66">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="52.8">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="52.8">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="66">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="66">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="66">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="52.8">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="66">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="52.8">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="79.2">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="66">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/docs/project_tracking/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/project_tracking/Unit_Test_Plan_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\infosys\ai-career-companion\docs\project_tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA471FE1-7874-4EE3-96A7-C0A35F70E343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1424DEA-B88C-48BD-A0BB-A545C4240A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="325">
   <si>
     <t>Actual Result</t>
   </si>
@@ -589,6 +589,462 @@
   </si>
   <si>
     <t>Existing M2 workflows remained functional</t>
+  </si>
+  <si>
+    <t>Application Tracker Access</t>
+  </si>
+  <si>
+    <t>Open the Applications section from the Career Companion dashboard</t>
+  </si>
+  <si>
+    <t>Application Tracker module is available</t>
+  </si>
+  <si>
+    <t>Application Tracker should open successfully</t>
+  </si>
+  <si>
+    <t>Application Tracker opened successfully</t>
+  </si>
+  <si>
+    <t>New Application Creation</t>
+  </si>
+  <si>
+    <t>Click “Track New Application” and enter application details</t>
+  </si>
+  <si>
+    <t>Valid job and application information provided</t>
+  </si>
+  <si>
+    <t>New application should be created and displayed in the tracker</t>
+  </si>
+  <si>
+    <t>Application was created and displayed successfully</t>
+  </si>
+  <si>
+    <t>Application Record Validation</t>
+  </si>
+  <si>
+    <t>Submit an application with required and optional fields</t>
+  </si>
+  <si>
+    <t>Application data contains valid and invalid values</t>
+  </si>
+  <si>
+    <t>System should validate application information before saving</t>
+  </si>
+  <si>
+    <t>Application data validation worked as expected</t>
+  </si>
+  <si>
+    <t>Application Status – Saved</t>
+  </si>
+  <si>
+    <t>Create an application with Saved status</t>
+  </si>
+  <si>
+    <t>New application is being tracked</t>
+  </si>
+  <si>
+    <t>Application should appear under Saved status</t>
+  </si>
+  <si>
+    <t>Application was displayed under Saved status</t>
+  </si>
+  <si>
+    <t>Application Status Workflow</t>
+  </si>
+  <si>
+    <t>Change application status through available workflow stages</t>
+  </si>
+  <si>
+    <t>Application record exists</t>
+  </si>
+  <si>
+    <t>Status should update correctly through the defined lifecycle</t>
+  </si>
+  <si>
+    <t>Application status workflow operated successfully</t>
+  </si>
+  <si>
+    <t>Application Status Persistence</t>
+  </si>
+  <si>
+    <t>Update application status and reload the Applications page</t>
+  </si>
+  <si>
+    <t>Existing application has an updated status</t>
+  </si>
+  <si>
+    <t>Updated status should remain available after reload</t>
+  </si>
+  <si>
+    <t>Updated status was retained successfully</t>
+  </si>
+  <si>
+    <t>Application Dashboard Metrics</t>
+  </si>
+  <si>
+    <t>Open the Tracker &amp; Dashboard tab</t>
+  </si>
+  <si>
+    <t>Applications are available in the tracker</t>
+  </si>
+  <si>
+    <t>Total, active, upcoming deadline, interview and outcome metrics should be displayed</t>
+  </si>
+  <si>
+    <t>Application dashboard metrics were displayed successfully</t>
+  </si>
+  <si>
+    <t>Application Status Filtering</t>
+  </si>
+  <si>
+    <t>Select different application status filters</t>
+  </si>
+  <si>
+    <t>Multiple application statuses are available</t>
+  </si>
+  <si>
+    <t>Tracker should display only applications matching the selected status</t>
+  </si>
+  <si>
+    <t>Status-based filtering worked successfully</t>
+  </si>
+  <si>
+    <t>Application Deadline Filtering</t>
+  </si>
+  <si>
+    <t>Apply Upcoming, Overdue and Has Deadline filters</t>
+  </si>
+  <si>
+    <t>Applications contain different deadline conditions</t>
+  </si>
+  <si>
+    <t>Applications should be filtered according to deadline status</t>
+  </si>
+  <si>
+    <t>Deadline filtering worked successfully</t>
+  </si>
+  <si>
+    <t>Application Without Deadline</t>
+  </si>
+  <si>
+    <t>Create or view an application without a deadline</t>
+  </si>
+  <si>
+    <t>Deadline is not provided</t>
+  </si>
+  <si>
+    <t>Application should remain trackable without causing an error</t>
+  </si>
+  <si>
+    <t>Application without a deadline was handled successfully</t>
+  </si>
+  <si>
+    <t>Application View</t>
+  </si>
+  <si>
+    <t>Select View for an existing application</t>
+  </si>
+  <si>
+    <t>Complete application information should be displayed</t>
+  </si>
+  <si>
+    <t>Application details were displayed successfully</t>
+  </si>
+  <si>
+    <t>Application Edit</t>
+  </si>
+  <si>
+    <t>Select Edit and modify application information</t>
+  </si>
+  <si>
+    <t>Existing application is available</t>
+  </si>
+  <si>
+    <t>Updated application information should be saved successfully</t>
+  </si>
+  <si>
+    <t>Application information was edited and saved successfully</t>
+  </si>
+  <si>
+    <t>Application Delete</t>
+  </si>
+  <si>
+    <t>Delete an existing application</t>
+  </si>
+  <si>
+    <t>Selected application should be removed from the tracker</t>
+  </si>
+  <si>
+    <t>Application was deleted successfully</t>
+  </si>
+  <si>
+    <t>Tailored Resume Navigation</t>
+  </si>
+  <si>
+    <t>Open Tailored Resume from Application Studio</t>
+  </si>
+  <si>
+    <t>Selected job and candidate profile are available</t>
+  </si>
+  <si>
+    <t>Tailored Resume section should open for the selected application</t>
+  </si>
+  <si>
+    <t>Tailored Resume section opened successfully</t>
+  </si>
+  <si>
+    <t>Tailored Resume Generation</t>
+  </si>
+  <si>
+    <t>Generate a tailored resume for a selected job</t>
+  </si>
+  <si>
+    <t>Candidate profile and job requirements are available</t>
+  </si>
+  <si>
+    <t>Resume should be customized according to the selected job</t>
+  </si>
+  <si>
+    <t>Tailored resume was generated successfully</t>
+  </si>
+  <si>
+    <t>Resume Information Verification</t>
+  </si>
+  <si>
+    <t>Review generated tailored resume content</t>
+  </si>
+  <si>
+    <t>Candidate profile contains verified information</t>
+  </si>
+  <si>
+    <t>Resume should use supported candidate skills, education and experience without inventing achievements</t>
+  </si>
+  <si>
+    <t>Generated resume content remained aligned with available candidate information</t>
+  </si>
+  <si>
+    <t>Personalized Cover Letter</t>
+  </si>
+  <si>
+    <t>Open Personalized Cover Letter for a selected job</t>
+  </si>
+  <si>
+    <t>Candidate profile and target job are available</t>
+  </si>
+  <si>
+    <t>Cover letter should be generated according to the candidate and job</t>
+  </si>
+  <si>
+    <t>Personalized cover letter was generated successfully</t>
+  </si>
+  <si>
+    <t>Cover Letter Content Validation</t>
+  </si>
+  <si>
+    <t>Review generated cover letter</t>
+  </si>
+  <si>
+    <t>Candidate and job information are available</t>
+  </si>
+  <si>
+    <t>Cover letter should use relevant candidate information without unsupported claims</t>
+  </si>
+  <si>
+    <t>Cover letter content was generated using available candidate and job information</t>
+  </si>
+  <si>
+    <t>Interview Scheduling</t>
+  </si>
+  <si>
+    <t>Add or view interview information for an application</t>
+  </si>
+  <si>
+    <t>Application has interview-related information</t>
+  </si>
+  <si>
+    <t>Interview schedule should be associated with the correct application</t>
+  </si>
+  <si>
+    <t>Interview information was associated with the application successfully</t>
+  </si>
+  <si>
+    <t>Application Materials</t>
+  </si>
+  <si>
+    <t>Open resume or cover letter materials associated with an application</t>
+  </si>
+  <si>
+    <t>Application contains generated materials</t>
+  </si>
+  <si>
+    <t>Associated application materials should be accessible</t>
+  </si>
+  <si>
+    <t>Application materials were accessible successfully</t>
+  </si>
+  <si>
+    <t>Application Tracker Persistence</t>
+  </si>
+  <si>
+    <t>Reload the application tracker after creating or editing records</t>
+  </si>
+  <si>
+    <t>Application records have been modified</t>
+  </si>
+  <si>
+    <t>Application records should remain available after reload</t>
+  </si>
+  <si>
+    <t>Application records persisted successfully</t>
+  </si>
+  <si>
+    <t>Application Management API</t>
+  </si>
+  <si>
+    <t>Perform application create, update, view and delete operations</t>
+  </si>
+  <si>
+    <t>Backend API is available</t>
+  </si>
+  <si>
+    <t>Application management requests should return successful responses</t>
+  </si>
+  <si>
+    <t>Application management API operations worked successfully</t>
+  </si>
+  <si>
+    <t>Application Error Handling</t>
+  </si>
+  <si>
+    <t>Submit invalid or incomplete application data</t>
+  </si>
+  <si>
+    <t>Required application information is missing or invalid</t>
+  </si>
+  <si>
+    <t>Invalid application requests were handled with validation responses</t>
+  </si>
+  <si>
+    <t>Application and Job Association</t>
+  </si>
+  <si>
+    <t>Create an application from a selected recommended job</t>
+  </si>
+  <si>
+    <t>Valid recommended job is available</t>
+  </si>
+  <si>
+    <t>Application should retain the correct job information</t>
+  </si>
+  <si>
+    <t>Application was associated with the selected job successfully</t>
+  </si>
+  <si>
+    <t>Application and Profile Association</t>
+  </si>
+  <si>
+    <t>Create an application for an existing candidate profile</t>
+  </si>
+  <si>
+    <t>Valid profile exists</t>
+  </si>
+  <si>
+    <t>Application should remain associated with the correct candidate profile</t>
+  </si>
+  <si>
+    <t>Application remained associated with the correct profile</t>
+  </si>
+  <si>
+    <t>Application Studio Integration</t>
+  </si>
+  <si>
+    <t>Navigate from selected job to Application Studio</t>
+  </si>
+  <si>
+    <t>Job has been selected from the recommended jobs workflow</t>
+  </si>
+  <si>
+    <t>Application Studio should use the selected job context</t>
+  </si>
+  <si>
+    <t>Selected job context was successfully passed to Application Studio</t>
+  </si>
+  <si>
+    <t>Application Tracker Integration</t>
+  </si>
+  <si>
+    <t>Create an application after completing job analysis</t>
+  </si>
+  <si>
+    <t>Matching and Skill Gap workflows are available</t>
+  </si>
+  <si>
+    <t>An analyzed job should be trackable as an application</t>
+  </si>
+  <si>
+    <t>Job analysis and application tracking workflows integrated successfully</t>
+  </si>
+  <si>
+    <t>Interview Preparation Integration</t>
+  </si>
+  <si>
+    <t>Open Interview Preparation for an application/job</t>
+  </si>
+  <si>
+    <t>Application and job information are available</t>
+  </si>
+  <si>
+    <t>Interview preparation should be accessible from the career workflow</t>
+  </si>
+  <si>
+    <t>Interview Preparation remained accessible successfully</t>
+  </si>
+  <si>
+    <t>End-to-End M4 Application Workflow</t>
+  </si>
+  <si>
+    <t>Find job → review match → analyze skill gap → generate materials → track application</t>
+  </si>
+  <si>
+    <t>Complete M1–M4 workflow is available</t>
+  </si>
+  <si>
+    <t>Candidate should be able to move from job discovery to application tracking without breaking the workflow</t>
+  </si>
+  <si>
+    <t>End-to-end application workflow completed successfully</t>
+  </si>
+  <si>
+    <t>M4 Regression Test</t>
+  </si>
+  <si>
+    <t>Run profile, resume, job matching and Skill Gap workflows after M4 implementation</t>
+  </si>
+  <si>
+    <t>Existing M1–M3 functionality is available</t>
+  </si>
+  <si>
+    <t>Existing functionality should continue working after M4 changes</t>
+  </si>
+  <si>
+    <t>Existing M1–M3 workflows remained functional</t>
+  </si>
+  <si>
+    <t>M4 Full Integration Test</t>
+  </si>
+  <si>
+    <t>Execute complete Career Companion workflow including application management</t>
+  </si>
+  <si>
+    <t>Backend and frontend modules are available</t>
+  </si>
+  <si>
+    <t>All integrated modules should operate together successfully</t>
+  </si>
+  <si>
+    <t>Full integrated Career Companion workflow operated successfully</t>
   </si>
 </sst>
 </file>
@@ -963,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -1673,6 +2129,626 @@
         <v>172</v>
       </c>
     </row>
+    <row r="36" spans="1:6" ht="79.2">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="52.8">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="52.8">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="39.6">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="52.8">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="66">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="79.2">
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="66">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="52.8">
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="52.8">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="52.8">
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="66">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="52.8">
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="66">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="52.8">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="92.4">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="52.8">
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="79.2">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="66">
+      <c r="A54" s="4">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="66">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="66">
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="66">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="66">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="66">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="52.8">
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="66">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="66">
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="66">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="92.4">
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="92.4">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="92.4">
+      <c r="A66" s="4">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
